--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E551"/>
+  <dimension ref="A1:E553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12005,6 +12005,48 @@
       <c r="E551" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="n">
+        <v>333.19</v>
+      </c>
+      <c r="C552" t="n">
+        <v>338.66</v>
+      </c>
+      <c r="D552" t="n">
+        <v>344.68</v>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="n">
+        <v>333.24</v>
+      </c>
+      <c r="C553" t="n">
+        <v>338.72</v>
+      </c>
+      <c r="D553" t="n">
+        <v>344.39</v>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12019,7 +12061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B691"/>
+  <dimension ref="A1:B694"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18932,6 +18974,36 @@
       </c>
       <c r="B691" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>2025-12-06 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B692" t="n">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B693" t="n">
+        <v>-0.58</v>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B694" t="n">
+        <v>-0.28</v>
       </c>
     </row>
   </sheetData>
@@ -19100,28 +19172,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3183553795960521</v>
+        <v>-0.3168972881470254</v>
       </c>
       <c r="J2" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K2" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2585842086084258</v>
+        <v>0.2581804329051427</v>
       </c>
       <c r="M2" t="n">
-        <v>2.892510325934103</v>
+        <v>2.888920158340776</v>
       </c>
       <c r="N2" t="n">
-        <v>12.87139443064293</v>
+        <v>12.83654799704984</v>
       </c>
       <c r="O2" t="n">
-        <v>3.587672564580403</v>
+        <v>3.582812861014351</v>
       </c>
       <c r="P2" t="n">
-        <v>339.7713512907369</v>
+        <v>339.7539580917246</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19178,28 +19250,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3689228717325599</v>
+        <v>-0.3691292716711833</v>
       </c>
       <c r="J3" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K3" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4679360643847933</v>
+        <v>0.4701964236409931</v>
       </c>
       <c r="M3" t="n">
-        <v>1.992987210020869</v>
+        <v>1.986699907192635</v>
       </c>
       <c r="N3" t="n">
-        <v>6.854722002236013</v>
+        <v>6.830127003630304</v>
       </c>
       <c r="O3" t="n">
-        <v>2.618152402408235</v>
+        <v>2.613451167255723</v>
       </c>
       <c r="P3" t="n">
-        <v>348.6491833524826</v>
+        <v>348.6516451192791</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19256,28 +19328,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2804940812204978</v>
+        <v>-0.2793946330441947</v>
       </c>
       <c r="J4" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="K4" t="n">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2344085180159512</v>
+        <v>0.2343261556315007</v>
       </c>
       <c r="M4" t="n">
-        <v>2.710618726602378</v>
+        <v>2.706010910668429</v>
       </c>
       <c r="N4" t="n">
-        <v>11.3818402941336</v>
+        <v>11.34737498105272</v>
       </c>
       <c r="O4" t="n">
-        <v>3.373698311072523</v>
+        <v>3.368586496002844</v>
       </c>
       <c r="P4" t="n">
-        <v>350.5469748366202</v>
+        <v>350.5338611111212</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19315,7 +19387,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E551"/>
+  <dimension ref="A1:E553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34195,6 +34267,60 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:14:56+00:00</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>-45.35991790697332,170.86299079754394</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>-45.36051783802177,170.8626963631578</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>-45.36113025297093,170.86246469911123</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-23 22:14:37+00:00</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>-45.359918093482136,170.86299137831014</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>-45.360518045931485,170.86269706992454</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>-45.36112932613963,170.8624612389083</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E553"/>
+  <dimension ref="A1:E554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12047,6 +12047,27 @@
       <c r="E553" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="n">
+        <v>332.58</v>
+      </c>
+      <c r="C554" t="n">
+        <v>338.31</v>
+      </c>
+      <c r="D554" t="n">
+        <v>343.91</v>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12061,7 +12082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B694"/>
+  <dimension ref="A1:B695"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19004,6 +19025,16 @@
       </c>
       <c r="B694" t="n">
         <v>-0.28</v>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B695" t="n">
+        <v>-0.09</v>
       </c>
     </row>
   </sheetData>
@@ -19172,28 +19203,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3168972881470254</v>
+        <v>-0.316422911672163</v>
       </c>
       <c r="J2" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K2" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2581804329051427</v>
+        <v>0.2583356269235301</v>
       </c>
       <c r="M2" t="n">
-        <v>2.888920158340776</v>
+        <v>2.885920051249106</v>
       </c>
       <c r="N2" t="n">
-        <v>12.83654799704984</v>
+        <v>12.81583771927529</v>
       </c>
       <c r="O2" t="n">
-        <v>3.582812861014351</v>
+        <v>3.579921468311182</v>
       </c>
       <c r="P2" t="n">
-        <v>339.7539580917246</v>
+        <v>339.7482859044006</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19250,28 +19281,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3691292716711833</v>
+        <v>-0.3693723426846947</v>
       </c>
       <c r="J3" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K3" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4701964236409931</v>
+        <v>0.4714974230639193</v>
       </c>
       <c r="M3" t="n">
-        <v>1.986699907192635</v>
+        <v>1.984197003890627</v>
       </c>
       <c r="N3" t="n">
-        <v>6.830127003630304</v>
+        <v>6.818432947676038</v>
       </c>
       <c r="O3" t="n">
-        <v>2.613451167255723</v>
+        <v>2.611212926529745</v>
       </c>
       <c r="P3" t="n">
-        <v>348.6516451192791</v>
+        <v>348.6545515541357</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19328,28 +19359,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2793946330441947</v>
+        <v>-0.2790974367170317</v>
       </c>
       <c r="J4" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="K4" t="n">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2343261556315007</v>
+        <v>0.2346467973998546</v>
       </c>
       <c r="M4" t="n">
-        <v>2.706010910668429</v>
+        <v>2.702515892036089</v>
       </c>
       <c r="N4" t="n">
-        <v>11.34737498105272</v>
+        <v>11.32783746514239</v>
       </c>
       <c r="O4" t="n">
-        <v>3.368586496002844</v>
+        <v>3.365685289081911</v>
       </c>
       <c r="P4" t="n">
-        <v>350.5338611111212</v>
+        <v>350.5303074921518</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19387,7 +19418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E553"/>
+  <dimension ref="A1:E554"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34321,6 +34352,33 @@
         </is>
       </c>
     </row>
+    <row r="554">
+      <c r="A554" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-07 22:20:28+00:00</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>-45.35991563156547,170.86298371219652</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>-45.36051662521502,170.86269224035195</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>-45.361127792073816,170.86245551167607</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E554"/>
+  <dimension ref="A1:E555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12068,6 +12068,27 @@
       <c r="E554" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="n">
+        <v>333.11</v>
+      </c>
+      <c r="C555" t="n">
+        <v>350.99</v>
+      </c>
+      <c r="D555" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B695"/>
+  <dimension ref="A1:B697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19035,6 +19056,26 @@
       </c>
       <c r="B695" t="n">
         <v>-0.09</v>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B696" t="n">
+        <v>-0.57</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2026-02-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B697" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -19203,28 +19244,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.316422911672163</v>
+        <v>-0.315730175578788</v>
       </c>
       <c r="J2" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K2" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2583356269235301</v>
+        <v>0.2581871611592698</v>
       </c>
       <c r="M2" t="n">
-        <v>2.885920051249106</v>
+        <v>2.883955842204692</v>
       </c>
       <c r="N2" t="n">
-        <v>12.81583771927529</v>
+        <v>12.79802257979889</v>
       </c>
       <c r="O2" t="n">
-        <v>3.579921468311182</v>
+        <v>3.57743240045132</v>
       </c>
       <c r="P2" t="n">
-        <v>339.7482859044006</v>
+        <v>339.7399822472737</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19281,28 +19322,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3693723426846947</v>
+        <v>-0.3645027052794855</v>
       </c>
       <c r="J3" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K3" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4714974230639193</v>
+        <v>0.4564760996455711</v>
       </c>
       <c r="M3" t="n">
-        <v>1.984197003890627</v>
+        <v>2.002702023629149</v>
       </c>
       <c r="N3" t="n">
-        <v>6.818432947676038</v>
+        <v>7.06892055885751</v>
       </c>
       <c r="O3" t="n">
-        <v>2.611212926529745</v>
+        <v>2.658744169501366</v>
       </c>
       <c r="P3" t="n">
-        <v>348.6545515541357</v>
+        <v>348.5961804085703</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19359,28 +19400,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2790974367170317</v>
+        <v>-0.2786739664109047</v>
       </c>
       <c r="J4" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="K4" t="n">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2346467973998546</v>
+        <v>0.2347925348667593</v>
       </c>
       <c r="M4" t="n">
-        <v>2.702515892036089</v>
+        <v>2.699613229175132</v>
       </c>
       <c r="N4" t="n">
-        <v>11.32783746514239</v>
+        <v>11.3093774360214</v>
       </c>
       <c r="O4" t="n">
-        <v>3.365685289081911</v>
+        <v>3.362941783025897</v>
       </c>
       <c r="P4" t="n">
-        <v>350.5303074921518</v>
+        <v>350.5252314577729</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19418,7 +19459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E554"/>
+  <dimension ref="A1:E555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34379,6 +34420,33 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>-45.35991760855919,170.862989868318</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>-45.360560563378144,170.86284160383389</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>-45.36112871890528,170.86245897187885</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E555"/>
+  <dimension ref="A1:E559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12081,12 +12081,96 @@
         <v>333.11</v>
       </c>
       <c r="C555" t="n">
-        <v>350.99</v>
+        <v>338.55</v>
       </c>
       <c r="D555" t="n">
         <v>344.2</v>
       </c>
       <c r="E555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="n">
+        <v>331.36</v>
+      </c>
+      <c r="C556" t="n">
+        <v>336.9</v>
+      </c>
+      <c r="D556" t="n">
+        <v>342.21</v>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>331.89</v>
+      </c>
+      <c r="C557" t="n">
+        <v>337.04</v>
+      </c>
+      <c r="D557" t="n">
+        <v>341.47</v>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>330.03</v>
+      </c>
+      <c r="C558" t="n">
+        <v>335.56</v>
+      </c>
+      <c r="D558" t="n">
+        <v>339.76</v>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>329.77</v>
+      </c>
+      <c r="C559" t="n">
+        <v>334.64</v>
+      </c>
+      <c r="D559" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="E559" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12103,7 +12187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B697"/>
+  <dimension ref="A1:B701"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19076,6 +19160,46 @@
       </c>
       <c r="B697" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B698" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B699" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B700" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B701" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -19244,28 +19368,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.315730175578788</v>
+        <v>-0.3166858941703556</v>
       </c>
       <c r="J2" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K2" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2581871611592698</v>
+        <v>0.2623295767499043</v>
       </c>
       <c r="M2" t="n">
-        <v>2.883955842204692</v>
+        <v>2.869255529994288</v>
       </c>
       <c r="N2" t="n">
-        <v>12.79802257979889</v>
+        <v>12.71439369254891</v>
       </c>
       <c r="O2" t="n">
-        <v>3.57743240045132</v>
+        <v>3.565724848126803</v>
       </c>
       <c r="P2" t="n">
-        <v>339.7399822472737</v>
+        <v>339.7514935296342</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19322,28 +19446,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3645027052794855</v>
+        <v>-0.3739831392178534</v>
       </c>
       <c r="J3" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K3" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4564760996455711</v>
+        <v>0.4804071870298515</v>
       </c>
       <c r="M3" t="n">
-        <v>2.002702023629149</v>
+        <v>1.986543710160049</v>
       </c>
       <c r="N3" t="n">
-        <v>7.06892055885751</v>
+        <v>6.819943685619235</v>
       </c>
       <c r="O3" t="n">
-        <v>2.658744169501366</v>
+        <v>2.611502189472418</v>
       </c>
       <c r="P3" t="n">
-        <v>348.5961804085703</v>
+        <v>348.7100351656055</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19400,28 +19524,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2786739664109047</v>
+        <v>-0.2825634535889948</v>
       </c>
       <c r="J4" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="K4" t="n">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2347925348667593</v>
+        <v>0.2419094983358444</v>
       </c>
       <c r="M4" t="n">
-        <v>2.699613229175132</v>
+        <v>2.696745455297137</v>
       </c>
       <c r="N4" t="n">
-        <v>11.3093774360214</v>
+        <v>11.28036670992357</v>
       </c>
       <c r="O4" t="n">
-        <v>3.362941783025897</v>
+        <v>3.358625717451048</v>
       </c>
       <c r="P4" t="n">
-        <v>350.5252314577729</v>
+        <v>350.5720475656753</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19459,7 +19583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E555"/>
+  <dimension ref="A1:E559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34433,7 +34557,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>-45.360560563378144,170.86284160383389</t>
+          <t>-45.36051745685395,170.8626950674188</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -34442,6 +34566,114 @@
         </is>
       </c>
       <c r="E555" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-24 22:20:23+00:00</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>-45.359911080748496,170.86296954150345</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>-45.36051173933488,170.8626756313359</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>-45.36112235892179,170.86243522773128</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-05 22:14:07+00:00</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>-45.35991305774298,170.8629756976239</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>-45.360512224457835,170.86267728045792</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>-45.36111999390156,170.86242639825068</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:14:12+00:00</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>-45.35990611961001,170.8629540931276</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>-45.36050709601398,170.86265984688362</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>-45.36111452878471,170.86240599499433</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:18+00:00</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>-45.35990514976314,170.86295107314467</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>-45.360503908061084,170.86264900979853</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>-45.36111305863568,170.86240050639975</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E559"/>
+  <dimension ref="A1:E562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12171,6 +12171,69 @@
         <v>339.3</v>
       </c>
       <c r="E559" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>328.83</v>
+      </c>
+      <c r="C560" t="n">
+        <v>334.84</v>
+      </c>
+      <c r="D560" t="n">
+        <v>338.28</v>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>327.92</v>
+      </c>
+      <c r="C561" t="n">
+        <v>333.61</v>
+      </c>
+      <c r="D561" t="n">
+        <v>336.38</v>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>327.35</v>
+      </c>
+      <c r="C562" t="n">
+        <v>333.23</v>
+      </c>
+      <c r="D562" t="n">
+        <v>336.25</v>
+      </c>
+      <c r="E562" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12187,7 +12250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B701"/>
+  <dimension ref="A1:B706"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19200,6 +19263,56 @@
       </c>
       <c r="B701" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B702" t="n">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>2026-03-28 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B703" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>2026-04-05 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B704" t="n">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B705" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B706" t="n">
+        <v>-0.05</v>
       </c>
     </row>
   </sheetData>
@@ -19368,28 +19481,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3166858941703556</v>
+        <v>-0.3205711307692933</v>
       </c>
       <c r="J2" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K2" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2623295767499043</v>
+        <v>0.2685082135908941</v>
       </c>
       <c r="M2" t="n">
-        <v>2.869255529994288</v>
+        <v>2.87066381737883</v>
       </c>
       <c r="N2" t="n">
-        <v>12.71439369254891</v>
+        <v>12.70527660622356</v>
       </c>
       <c r="O2" t="n">
-        <v>3.565724848126803</v>
+        <v>3.564446185064877</v>
       </c>
       <c r="P2" t="n">
-        <v>339.7514935296342</v>
+        <v>339.7983814573249</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19446,28 +19559,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3739831392178534</v>
+        <v>-0.3797251402913112</v>
       </c>
       <c r="J3" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K3" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4804071870298515</v>
+        <v>0.486375284279549</v>
       </c>
       <c r="M3" t="n">
-        <v>1.986543710160049</v>
+        <v>2.001103964163749</v>
       </c>
       <c r="N3" t="n">
-        <v>6.819943685619235</v>
+        <v>6.910294337916604</v>
       </c>
       <c r="O3" t="n">
-        <v>2.611502189472418</v>
+        <v>2.628743870733055</v>
       </c>
       <c r="P3" t="n">
-        <v>348.7100351656055</v>
+        <v>348.7793282063981</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19524,28 +19637,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2825634535889948</v>
+        <v>-0.2897429961535903</v>
       </c>
       <c r="J4" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="K4" t="n">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2419094983358444</v>
+        <v>0.2501734130085962</v>
       </c>
       <c r="M4" t="n">
-        <v>2.696745455297137</v>
+        <v>2.713059045457652</v>
       </c>
       <c r="N4" t="n">
-        <v>11.28036670992357</v>
+        <v>11.41902444816109</v>
       </c>
       <c r="O4" t="n">
-        <v>3.358625717451048</v>
+        <v>3.379204706459952</v>
       </c>
       <c r="P4" t="n">
-        <v>350.5720475656753</v>
+        <v>350.6586899921739</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19583,7 +19696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E559"/>
+  <dimension ref="A1:E562"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34679,6 +34792,87 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:14:22+00:00</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>-45.35990164339306,170.86294015474573</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>-45.3605046010944,170.8626513656865</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>-45.361109798739136,170.8623883360389</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-13 22:19:57+00:00</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>-45.35989824892742,170.86292958480763</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>-45.360500338938685,170.86263687697647</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>-45.36110372637941,170.8623656657627</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>-45.35989612272319,170.86292296407782</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>-45.360499022174785,170.8626324007901</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>-45.36110331090201,170.86236411463872</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E562"/>
+  <dimension ref="A1:E567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12234,6 +12234,111 @@
         <v>336.25</v>
       </c>
       <c r="E562" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="n">
+        <v>326.98</v>
+      </c>
+      <c r="C563" t="n">
+        <v>333.45</v>
+      </c>
+      <c r="D563" t="n">
+        <v>336.42</v>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="n">
+        <v>327.61</v>
+      </c>
+      <c r="C564" t="n">
+        <v>333.52</v>
+      </c>
+      <c r="D564" t="n">
+        <v>336.1</v>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="n">
+        <v>327.31</v>
+      </c>
+      <c r="C565" t="n">
+        <v>333.44</v>
+      </c>
+      <c r="D565" t="n">
+        <v>335.98</v>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="n">
+        <v>328.76</v>
+      </c>
+      <c r="C566" t="n">
+        <v>334.54</v>
+      </c>
+      <c r="D566" t="n">
+        <v>336.66</v>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="n">
+        <v>329.43</v>
+      </c>
+      <c r="C567" t="n">
+        <v>335.28</v>
+      </c>
+      <c r="D567" t="n">
+        <v>337.48</v>
+      </c>
+      <c r="E567" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12250,7 +12355,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B706"/>
+  <dimension ref="A1:B713"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19313,6 +19418,76 @@
       </c>
       <c r="B706" t="n">
         <v>-0.05</v>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B707" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>0.11</v>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>2026-05-23 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>0.66</v>
       </c>
     </row>
   </sheetData>
@@ -19481,28 +19656,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3205711307692933</v>
+        <v>-0.3267796385605385</v>
       </c>
       <c r="J2" t="n">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="K2" t="n">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2685082135908941</v>
+        <v>0.2785108171761311</v>
       </c>
       <c r="M2" t="n">
-        <v>2.87066381737883</v>
+        <v>2.872765452241677</v>
       </c>
       <c r="N2" t="n">
-        <v>12.70527660622356</v>
+        <v>12.68997118295422</v>
       </c>
       <c r="O2" t="n">
-        <v>3.564446185064877</v>
+        <v>3.562298581387335</v>
       </c>
       <c r="P2" t="n">
-        <v>339.7983814573249</v>
+        <v>339.8735077869938</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19559,28 +19734,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3797251402913112</v>
+        <v>-0.388579781887584</v>
       </c>
       <c r="J3" t="n">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="K3" t="n">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="L3" t="n">
-        <v>0.486375284279549</v>
+        <v>0.4960966245171784</v>
       </c>
       <c r="M3" t="n">
-        <v>2.001103964163749</v>
+        <v>2.023438991310192</v>
       </c>
       <c r="N3" t="n">
-        <v>6.910294337916604</v>
+        <v>7.035651171191523</v>
       </c>
       <c r="O3" t="n">
-        <v>2.628743870733055</v>
+        <v>2.652480192422089</v>
       </c>
       <c r="P3" t="n">
-        <v>348.7793282063981</v>
+        <v>348.8864862068584</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19637,28 +19812,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2897429961535903</v>
+        <v>-0.3020643514214663</v>
       </c>
       <c r="J4" t="n">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="K4" t="n">
-        <v>561</v>
+        <v>566</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2501734130085962</v>
+        <v>0.2639545744626483</v>
       </c>
       <c r="M4" t="n">
-        <v>2.713059045457652</v>
+        <v>2.742258429308161</v>
       </c>
       <c r="N4" t="n">
-        <v>11.41902444816109</v>
+        <v>11.67178494138916</v>
       </c>
       <c r="O4" t="n">
-        <v>3.379204706459952</v>
+        <v>3.416399411864654</v>
       </c>
       <c r="P4" t="n">
-        <v>350.6586899921739</v>
+        <v>350.8078135459721</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19696,7 +19871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E562"/>
+  <dimension ref="A1:E567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34873,6 +35048,141 @@
         </is>
       </c>
     </row>
+    <row r="563">
+      <c r="A563" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:14:08+00:00</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>-45.35989474255535,170.86291866641142</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>-45.3604997845118,170.8626349922664</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>-45.361103854218605,170.8623661430316</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:14:17+00:00</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>-45.359897092570776,170.86292598405979</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>-45.36050002707358,170.86263581682704</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>-45.36110283150498,170.8623623248803</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:13:52+00:00</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>-45.35989597351587,170.86292249946527</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>-45.36049974986013,170.86263487447204</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>-45.361102447987335,170.8623608930736</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:30+00:00</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>-45.35990138228034,170.8629393416735</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>-45.3605035615444,170.8626478318546</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>-45.36110462125376,170.8623690066452</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>-45.35990388150173,170.86294712393638</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>-45.36050612576756,170.8626565486402</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>-45.36110724195664,170.86237879065882</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0484/nzd0484.xlsx
+++ b/data/nzd0484/nzd0484.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E567"/>
+  <dimension ref="A1:E569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12339,6 +12339,48 @@
         <v>337.48</v>
       </c>
       <c r="E567" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="n">
+        <v>328.81</v>
+      </c>
+      <c r="C568" t="n">
+        <v>335.25</v>
+      </c>
+      <c r="D568" t="n">
+        <v>337.38</v>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="n">
+        <v>329.38</v>
+      </c>
+      <c r="C569" t="n">
+        <v>336</v>
+      </c>
+      <c r="D569" t="n">
+        <v>337.78</v>
+      </c>
+      <c r="E569" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12355,7 +12397,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B713"/>
+  <dimension ref="A1:B715"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19488,6 +19530,26 @@
       </c>
       <c r="B713" t="n">
         <v>0.66</v>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>-0.71</v>
       </c>
     </row>
   </sheetData>
@@ -19656,28 +19718,28 @@
         <v>0.07290000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3267796385605385</v>
+        <v>-0.3283368980875597</v>
       </c>
       <c r="J2" t="n">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K2" t="n">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2785108171761311</v>
+        <v>0.2817726672670322</v>
       </c>
       <c r="M2" t="n">
-        <v>2.872765452241677</v>
+        <v>2.86952244360916</v>
       </c>
       <c r="N2" t="n">
-        <v>12.68997118295422</v>
+        <v>12.65982740733252</v>
       </c>
       <c r="O2" t="n">
-        <v>3.562298581387335</v>
+        <v>3.558065121288889</v>
       </c>
       <c r="P2" t="n">
-        <v>339.8735077869938</v>
+        <v>339.8924278935469</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19734,28 +19796,28 @@
         <v>0.0818</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.388579781887584</v>
+        <v>-0.390772196261729</v>
       </c>
       <c r="J3" t="n">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K3" t="n">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4960966245171784</v>
+        <v>0.499840961434436</v>
       </c>
       <c r="M3" t="n">
-        <v>2.023438991310192</v>
+        <v>2.026331624182521</v>
       </c>
       <c r="N3" t="n">
-        <v>7.035651171191523</v>
+        <v>7.039615314098498</v>
       </c>
       <c r="O3" t="n">
-        <v>2.652480192422089</v>
+        <v>2.653227339316874</v>
       </c>
       <c r="P3" t="n">
-        <v>348.8864862068584</v>
+        <v>348.9131233116815</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19812,28 +19874,28 @@
         <v>0.0785</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3020643514214663</v>
+        <v>-0.3060175533634437</v>
       </c>
       <c r="J4" t="n">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="K4" t="n">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2639545744626483</v>
+        <v>0.269026685755151</v>
       </c>
       <c r="M4" t="n">
-        <v>2.742258429308161</v>
+        <v>2.74975967528972</v>
       </c>
       <c r="N4" t="n">
-        <v>11.67178494138916</v>
+        <v>11.72260619643865</v>
       </c>
       <c r="O4" t="n">
-        <v>3.416399411864654</v>
+        <v>3.423829171620373</v>
       </c>
       <c r="P4" t="n">
-        <v>350.8078135459721</v>
+        <v>350.855845458975</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19871,7 +19933,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E567"/>
+  <dimension ref="A1:E569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35183,6 +35245,60 @@
         </is>
       </c>
     </row>
+    <row r="568">
+      <c r="A568" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:13:41+00:00</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>-45.35990156878943,170.86293992243938</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>-45.360506021812576,170.862656195257</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>-45.36110692235875,170.8623775974864</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:13:59+00:00</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>-45.359903694992695,170.86294654317044</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>-45.36050862068675,170.8626650298378</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>-45.36110820075016,170.86238237017625</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
